--- a/408-sfe-serafin-lot-2/ig/ValueSet-tddui-care-plan-supportingInfo-vs.xlsx
+++ b/408-sfe-serafin-lot-2/ig/ValueSet-tddui-care-plan-supportingInfo-vs.xlsx
@@ -61,7 +61,7 @@
     <t>Date</t>
   </si>
   <si>
-    <t>2026-01-05T13:05:46+00:00</t>
+    <t>2026-01-09T15:52:02+00:00</t>
   </si>
   <si>
     <t>Publisher</t>

--- a/408-sfe-serafin-lot-2/ig/ValueSet-tddui-care-plan-supportingInfo-vs.xlsx
+++ b/408-sfe-serafin-lot-2/ig/ValueSet-tddui-care-plan-supportingInfo-vs.xlsx
@@ -61,7 +61,7 @@
     <t>Date</t>
   </si>
   <si>
-    <t>2026-01-09T15:52:02+00:00</t>
+    <t>2026-01-12T15:02:59+00:00</t>
   </si>
   <si>
     <t>Publisher</t>

--- a/408-sfe-serafin-lot-2/ig/ValueSet-tddui-care-plan-supportingInfo-vs.xlsx
+++ b/408-sfe-serafin-lot-2/ig/ValueSet-tddui-care-plan-supportingInfo-vs.xlsx
@@ -61,7 +61,7 @@
     <t>Date</t>
   </si>
   <si>
-    <t>2026-01-12T15:02:59+00:00</t>
+    <t>2026-01-12T15:45:07+00:00</t>
   </si>
   <si>
     <t>Publisher</t>

--- a/408-sfe-serafin-lot-2/ig/ValueSet-tddui-care-plan-supportingInfo-vs.xlsx
+++ b/408-sfe-serafin-lot-2/ig/ValueSet-tddui-care-plan-supportingInfo-vs.xlsx
@@ -61,7 +61,7 @@
     <t>Date</t>
   </si>
   <si>
-    <t>2026-01-12T15:45:07+00:00</t>
+    <t>2026-01-13T07:15:40+00:00</t>
   </si>
   <si>
     <t>Publisher</t>

--- a/408-sfe-serafin-lot-2/ig/ValueSet-tddui-care-plan-supportingInfo-vs.xlsx
+++ b/408-sfe-serafin-lot-2/ig/ValueSet-tddui-care-plan-supportingInfo-vs.xlsx
@@ -61,7 +61,7 @@
     <t>Date</t>
   </si>
   <si>
-    <t>2026-01-13T07:15:40+00:00</t>
+    <t>2026-01-13T10:01:23+00:00</t>
   </si>
   <si>
     <t>Publisher</t>

--- a/408-sfe-serafin-lot-2/ig/ValueSet-tddui-care-plan-supportingInfo-vs.xlsx
+++ b/408-sfe-serafin-lot-2/ig/ValueSet-tddui-care-plan-supportingInfo-vs.xlsx
@@ -61,7 +61,7 @@
     <t>Date</t>
   </si>
   <si>
-    <t>2026-01-13T10:01:23+00:00</t>
+    <t>2026-01-14T09:54:26+00:00</t>
   </si>
   <si>
     <t>Publisher</t>

--- a/408-sfe-serafin-lot-2/ig/ValueSet-tddui-care-plan-supportingInfo-vs.xlsx
+++ b/408-sfe-serafin-lot-2/ig/ValueSet-tddui-care-plan-supportingInfo-vs.xlsx
@@ -61,7 +61,7 @@
     <t>Date</t>
   </si>
   <si>
-    <t>2026-01-14T09:54:26+00:00</t>
+    <t>2026-01-14T10:22:18+00:00</t>
   </si>
   <si>
     <t>Publisher</t>

--- a/408-sfe-serafin-lot-2/ig/ValueSet-tddui-care-plan-supportingInfo-vs.xlsx
+++ b/408-sfe-serafin-lot-2/ig/ValueSet-tddui-care-plan-supportingInfo-vs.xlsx
@@ -61,7 +61,7 @@
     <t>Date</t>
   </si>
   <si>
-    <t>2026-01-14T10:22:18+00:00</t>
+    <t>2026-01-15T16:20:03+00:00</t>
   </si>
   <si>
     <t>Publisher</t>

--- a/408-sfe-serafin-lot-2/ig/ValueSet-tddui-care-plan-supportingInfo-vs.xlsx
+++ b/408-sfe-serafin-lot-2/ig/ValueSet-tddui-care-plan-supportingInfo-vs.xlsx
@@ -61,7 +61,7 @@
     <t>Date</t>
   </si>
   <si>
-    <t>2026-01-15T16:20:03+00:00</t>
+    <t>2026-01-20T14:52:30+00:00</t>
   </si>
   <si>
     <t>Publisher</t>

--- a/408-sfe-serafin-lot-2/ig/ValueSet-tddui-care-plan-supportingInfo-vs.xlsx
+++ b/408-sfe-serafin-lot-2/ig/ValueSet-tddui-care-plan-supportingInfo-vs.xlsx
@@ -61,7 +61,7 @@
     <t>Date</t>
   </si>
   <si>
-    <t>2026-01-20T14:52:30+00:00</t>
+    <t>2026-01-23T15:15:31+00:00</t>
   </si>
   <si>
     <t>Publisher</t>

--- a/408-sfe-serafin-lot-2/ig/ValueSet-tddui-care-plan-supportingInfo-vs.xlsx
+++ b/408-sfe-serafin-lot-2/ig/ValueSet-tddui-care-plan-supportingInfo-vs.xlsx
@@ -61,7 +61,7 @@
     <t>Date</t>
   </si>
   <si>
-    <t>2026-01-23T15:15:31+00:00</t>
+    <t>2026-01-26T08:31:39+00:00</t>
   </si>
   <si>
     <t>Publisher</t>

--- a/408-sfe-serafin-lot-2/ig/ValueSet-tddui-care-plan-supportingInfo-vs.xlsx
+++ b/408-sfe-serafin-lot-2/ig/ValueSet-tddui-care-plan-supportingInfo-vs.xlsx
@@ -61,7 +61,7 @@
     <t>Date</t>
   </si>
   <si>
-    <t>2026-01-26T08:31:39+00:00</t>
+    <t>2026-01-27T09:38:15+00:00</t>
   </si>
   <si>
     <t>Publisher</t>

--- a/408-sfe-serafin-lot-2/ig/ValueSet-tddui-care-plan-supportingInfo-vs.xlsx
+++ b/408-sfe-serafin-lot-2/ig/ValueSet-tddui-care-plan-supportingInfo-vs.xlsx
@@ -61,7 +61,7 @@
     <t>Date</t>
   </si>
   <si>
-    <t>2026-01-27T09:38:15+00:00</t>
+    <t>2026-01-27T09:56:15+00:00</t>
   </si>
   <si>
     <t>Publisher</t>

--- a/408-sfe-serafin-lot-2/ig/ValueSet-tddui-care-plan-supportingInfo-vs.xlsx
+++ b/408-sfe-serafin-lot-2/ig/ValueSet-tddui-care-plan-supportingInfo-vs.xlsx
@@ -61,7 +61,7 @@
     <t>Date</t>
   </si>
   <si>
-    <t>2026-01-27T09:56:15+00:00</t>
+    <t>2026-01-27T15:18:17+00:00</t>
   </si>
   <si>
     <t>Publisher</t>

--- a/408-sfe-serafin-lot-2/ig/ValueSet-tddui-care-plan-supportingInfo-vs.xlsx
+++ b/408-sfe-serafin-lot-2/ig/ValueSet-tddui-care-plan-supportingInfo-vs.xlsx
@@ -61,7 +61,7 @@
     <t>Date</t>
   </si>
   <si>
-    <t>2026-01-27T15:18:17+00:00</t>
+    <t>2026-01-27T15:24:55+00:00</t>
   </si>
   <si>
     <t>Publisher</t>

--- a/408-sfe-serafin-lot-2/ig/ValueSet-tddui-care-plan-supportingInfo-vs.xlsx
+++ b/408-sfe-serafin-lot-2/ig/ValueSet-tddui-care-plan-supportingInfo-vs.xlsx
@@ -61,7 +61,7 @@
     <t>Date</t>
   </si>
   <si>
-    <t>2026-01-27T15:24:55+00:00</t>
+    <t>2026-01-27T16:32:30+00:00</t>
   </si>
   <si>
     <t>Publisher</t>

--- a/408-sfe-serafin-lot-2/ig/ValueSet-tddui-care-plan-supportingInfo-vs.xlsx
+++ b/408-sfe-serafin-lot-2/ig/ValueSet-tddui-care-plan-supportingInfo-vs.xlsx
@@ -61,7 +61,7 @@
     <t>Date</t>
   </si>
   <si>
-    <t>2026-01-27T16:32:30+00:00</t>
+    <t>2026-01-28T15:17:38+00:00</t>
   </si>
   <si>
     <t>Publisher</t>

--- a/408-sfe-serafin-lot-2/ig/ValueSet-tddui-care-plan-supportingInfo-vs.xlsx
+++ b/408-sfe-serafin-lot-2/ig/ValueSet-tddui-care-plan-supportingInfo-vs.xlsx
@@ -61,7 +61,7 @@
     <t>Date</t>
   </si>
   <si>
-    <t>2026-01-28T15:17:38+00:00</t>
+    <t>2026-01-29T09:55:11+00:00</t>
   </si>
   <si>
     <t>Publisher</t>

--- a/408-sfe-serafin-lot-2/ig/ValueSet-tddui-care-plan-supportingInfo-vs.xlsx
+++ b/408-sfe-serafin-lot-2/ig/ValueSet-tddui-care-plan-supportingInfo-vs.xlsx
@@ -61,7 +61,7 @@
     <t>Date</t>
   </si>
   <si>
-    <t>2026-01-29T09:55:11+00:00</t>
+    <t>2026-01-29T10:16:57+00:00</t>
   </si>
   <si>
     <t>Publisher</t>

--- a/408-sfe-serafin-lot-2/ig/ValueSet-tddui-care-plan-supportingInfo-vs.xlsx
+++ b/408-sfe-serafin-lot-2/ig/ValueSet-tddui-care-plan-supportingInfo-vs.xlsx
@@ -61,7 +61,7 @@
     <t>Date</t>
   </si>
   <si>
-    <t>2026-01-29T10:16:57+00:00</t>
+    <t>2026-01-29T10:29:35+00:00</t>
   </si>
   <si>
     <t>Publisher</t>

--- a/408-sfe-serafin-lot-2/ig/ValueSet-tddui-care-plan-supportingInfo-vs.xlsx
+++ b/408-sfe-serafin-lot-2/ig/ValueSet-tddui-care-plan-supportingInfo-vs.xlsx
@@ -61,7 +61,7 @@
     <t>Date</t>
   </si>
   <si>
-    <t>2026-01-29T10:29:35+00:00</t>
+    <t>2026-01-29T10:42:42+00:00</t>
   </si>
   <si>
     <t>Publisher</t>

--- a/408-sfe-serafin-lot-2/ig/ValueSet-tddui-care-plan-supportingInfo-vs.xlsx
+++ b/408-sfe-serafin-lot-2/ig/ValueSet-tddui-care-plan-supportingInfo-vs.xlsx
@@ -61,7 +61,7 @@
     <t>Date</t>
   </si>
   <si>
-    <t>2026-01-29T10:42:42+00:00</t>
+    <t>2026-01-29T15:10:00+00:00</t>
   </si>
   <si>
     <t>Publisher</t>

--- a/408-sfe-serafin-lot-2/ig/ValueSet-tddui-care-plan-supportingInfo-vs.xlsx
+++ b/408-sfe-serafin-lot-2/ig/ValueSet-tddui-care-plan-supportingInfo-vs.xlsx
@@ -61,7 +61,7 @@
     <t>Date</t>
   </si>
   <si>
-    <t>2026-01-29T15:10:00+00:00</t>
+    <t>2026-01-29T16:09:55+00:00</t>
   </si>
   <si>
     <t>Publisher</t>

--- a/408-sfe-serafin-lot-2/ig/ValueSet-tddui-care-plan-supportingInfo-vs.xlsx
+++ b/408-sfe-serafin-lot-2/ig/ValueSet-tddui-care-plan-supportingInfo-vs.xlsx
@@ -61,7 +61,7 @@
     <t>Date</t>
   </si>
   <si>
-    <t>2026-01-29T16:09:55+00:00</t>
+    <t>2026-01-30T07:44:02+00:00</t>
   </si>
   <si>
     <t>Publisher</t>

--- a/408-sfe-serafin-lot-2/ig/ValueSet-tddui-care-plan-supportingInfo-vs.xlsx
+++ b/408-sfe-serafin-lot-2/ig/ValueSet-tddui-care-plan-supportingInfo-vs.xlsx
@@ -61,7 +61,7 @@
     <t>Date</t>
   </si>
   <si>
-    <t>2026-01-30T07:44:02+00:00</t>
+    <t>2026-01-30T08:34:52+00:00</t>
   </si>
   <si>
     <t>Publisher</t>

--- a/408-sfe-serafin-lot-2/ig/ValueSet-tddui-care-plan-supportingInfo-vs.xlsx
+++ b/408-sfe-serafin-lot-2/ig/ValueSet-tddui-care-plan-supportingInfo-vs.xlsx
@@ -61,7 +61,7 @@
     <t>Date</t>
   </si>
   <si>
-    <t>2026-01-30T08:34:52+00:00</t>
+    <t>2026-02-03T08:44:10+00:00</t>
   </si>
   <si>
     <t>Publisher</t>

--- a/408-sfe-serafin-lot-2/ig/ValueSet-tddui-care-plan-supportingInfo-vs.xlsx
+++ b/408-sfe-serafin-lot-2/ig/ValueSet-tddui-care-plan-supportingInfo-vs.xlsx
@@ -61,7 +61,7 @@
     <t>Date</t>
   </si>
   <si>
-    <t>2026-02-03T08:44:10+00:00</t>
+    <t>2026-02-03T10:58:54+00:00</t>
   </si>
   <si>
     <t>Publisher</t>

--- a/408-sfe-serafin-lot-2/ig/ValueSet-tddui-care-plan-supportingInfo-vs.xlsx
+++ b/408-sfe-serafin-lot-2/ig/ValueSet-tddui-care-plan-supportingInfo-vs.xlsx
@@ -61,7 +61,7 @@
     <t>Date</t>
   </si>
   <si>
-    <t>2026-02-03T10:58:54+00:00</t>
+    <t>2026-02-03T16:58:15+00:00</t>
   </si>
   <si>
     <t>Publisher</t>

--- a/408-sfe-serafin-lot-2/ig/ValueSet-tddui-care-plan-supportingInfo-vs.xlsx
+++ b/408-sfe-serafin-lot-2/ig/ValueSet-tddui-care-plan-supportingInfo-vs.xlsx
@@ -61,7 +61,7 @@
     <t>Date</t>
   </si>
   <si>
-    <t>2026-02-03T16:58:15+00:00</t>
+    <t>2026-02-04T12:57:04+00:00</t>
   </si>
   <si>
     <t>Publisher</t>

--- a/408-sfe-serafin-lot-2/ig/ValueSet-tddui-care-plan-supportingInfo-vs.xlsx
+++ b/408-sfe-serafin-lot-2/ig/ValueSet-tddui-care-plan-supportingInfo-vs.xlsx
@@ -61,7 +61,7 @@
     <t>Date</t>
   </si>
   <si>
-    <t>2026-02-04T12:57:04+00:00</t>
+    <t>2026-02-05T15:47:09+00:00</t>
   </si>
   <si>
     <t>Publisher</t>

--- a/408-sfe-serafin-lot-2/ig/ValueSet-tddui-care-plan-supportingInfo-vs.xlsx
+++ b/408-sfe-serafin-lot-2/ig/ValueSet-tddui-care-plan-supportingInfo-vs.xlsx
@@ -61,7 +61,7 @@
     <t>Date</t>
   </si>
   <si>
-    <t>2026-02-05T15:47:09+00:00</t>
+    <t>2026-02-06T15:48:36+00:00</t>
   </si>
   <si>
     <t>Publisher</t>

--- a/408-sfe-serafin-lot-2/ig/ValueSet-tddui-care-plan-supportingInfo-vs.xlsx
+++ b/408-sfe-serafin-lot-2/ig/ValueSet-tddui-care-plan-supportingInfo-vs.xlsx
@@ -61,7 +61,7 @@
     <t>Date</t>
   </si>
   <si>
-    <t>2026-02-06T15:48:36+00:00</t>
+    <t>2026-02-09T09:51:45+00:00</t>
   </si>
   <si>
     <t>Publisher</t>

--- a/408-sfe-serafin-lot-2/ig/ValueSet-tddui-care-plan-supportingInfo-vs.xlsx
+++ b/408-sfe-serafin-lot-2/ig/ValueSet-tddui-care-plan-supportingInfo-vs.xlsx
@@ -61,7 +61,7 @@
     <t>Date</t>
   </si>
   <si>
-    <t>2026-02-09T09:51:45+00:00</t>
+    <t>2026-02-10T14:13:53+00:00</t>
   </si>
   <si>
     <t>Publisher</t>

--- a/408-sfe-serafin-lot-2/ig/ValueSet-tddui-care-plan-supportingInfo-vs.xlsx
+++ b/408-sfe-serafin-lot-2/ig/ValueSet-tddui-care-plan-supportingInfo-vs.xlsx
@@ -61,7 +61,7 @@
     <t>Date</t>
   </si>
   <si>
-    <t>2026-02-10T14:13:53+00:00</t>
+    <t>2026-02-11T12:59:12+00:00</t>
   </si>
   <si>
     <t>Publisher</t>

--- a/408-sfe-serafin-lot-2/ig/ValueSet-tddui-care-plan-supportingInfo-vs.xlsx
+++ b/408-sfe-serafin-lot-2/ig/ValueSet-tddui-care-plan-supportingInfo-vs.xlsx
@@ -61,7 +61,7 @@
     <t>Date</t>
   </si>
   <si>
-    <t>2026-02-11T12:59:12+00:00</t>
+    <t>2026-02-11T14:29:56+00:00</t>
   </si>
   <si>
     <t>Publisher</t>

--- a/408-sfe-serafin-lot-2/ig/ValueSet-tddui-care-plan-supportingInfo-vs.xlsx
+++ b/408-sfe-serafin-lot-2/ig/ValueSet-tddui-care-plan-supportingInfo-vs.xlsx
@@ -61,7 +61,7 @@
     <t>Date</t>
   </si>
   <si>
-    <t>2026-02-11T14:29:56+00:00</t>
+    <t>2026-02-12T14:43:45+00:00</t>
   </si>
   <si>
     <t>Publisher</t>

--- a/408-sfe-serafin-lot-2/ig/ValueSet-tddui-care-plan-supportingInfo-vs.xlsx
+++ b/408-sfe-serafin-lot-2/ig/ValueSet-tddui-care-plan-supportingInfo-vs.xlsx
@@ -61,7 +61,7 @@
     <t>Date</t>
   </si>
   <si>
-    <t>2026-02-12T14:43:45+00:00</t>
+    <t>2026-02-13T10:11:04+00:00</t>
   </si>
   <si>
     <t>Publisher</t>

--- a/408-sfe-serafin-lot-2/ig/ValueSet-tddui-care-plan-supportingInfo-vs.xlsx
+++ b/408-sfe-serafin-lot-2/ig/ValueSet-tddui-care-plan-supportingInfo-vs.xlsx
@@ -61,7 +61,7 @@
     <t>Date</t>
   </si>
   <si>
-    <t>2026-02-13T10:11:04+00:00</t>
+    <t>2026-02-16T16:27:33+00:00</t>
   </si>
   <si>
     <t>Publisher</t>

--- a/408-sfe-serafin-lot-2/ig/ValueSet-tddui-care-plan-supportingInfo-vs.xlsx
+++ b/408-sfe-serafin-lot-2/ig/ValueSet-tddui-care-plan-supportingInfo-vs.xlsx
@@ -61,7 +61,7 @@
     <t>Date</t>
   </si>
   <si>
-    <t>2026-02-16T16:27:33+00:00</t>
+    <t>2026-02-17T14:40:03+00:00</t>
   </si>
   <si>
     <t>Publisher</t>

--- a/408-sfe-serafin-lot-2/ig/ValueSet-tddui-care-plan-supportingInfo-vs.xlsx
+++ b/408-sfe-serafin-lot-2/ig/ValueSet-tddui-care-plan-supportingInfo-vs.xlsx
@@ -61,7 +61,7 @@
     <t>Date</t>
   </si>
   <si>
-    <t>2026-02-17T14:40:03+00:00</t>
+    <t>2026-02-19T13:12:21+00:00</t>
   </si>
   <si>
     <t>Publisher</t>
